--- a/entorno/mir-v2/archivos_de_prueba/Chaco_con_errores/DISP_SCP_2026_T1_Chaco_CON_ERRORES.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chaco_con_errores/DISP_SCP_2026_T1_Chaco_CON_ERRORES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="M Residencial" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="INSTRUCCIONES" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="LISTAS" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet name="ERRORES_ESPERADOS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M Residencial" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERRORES_ESPERADOS" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/entorno/mir-v2/archivos_de_prueba/Chaco_con_errores/DISP_SCP_2026_T1_Chaco_CON_ERRORES.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chaco_con_errores/DISP_SCP_2026_T1_Chaco_CON_ERRORES.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M Residencial" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERRORES_ESPERADOS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="M Residencial" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="ERRORES_ESPERADOS" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,10 +38,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="6">
@@ -99,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,11 +110,6 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -199,560 +189,503 @@
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>RUNAC</author>
+    <author>MIR</author>
   </authors>
   <commentList>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
         <t>Nombre del dispositvo
-Qué se espera: texto
-Máximo 120 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
         <t>Dependencia institucional
-Organismo, ministerio, secretaría, dirección o área estatal de la cual depende orgánica y formalmente el dispositivo de cuidado.
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.
+Organismo, ministerio, secretaría, dirección o área estatal de la cual depende orgánica y formalmente el dispositivo de cuidado.</t>
       </text>
     </comment>
     <comment ref="C4" authorId="0" shapeId="0">
       <text>
         <t>Tipo de gestión
-Carácter público o privado/asociativo de la administración de la institución de cuidado alternativo.
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Tipo de gestión".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Gubernamental, No gubernamental, Mixta.
+Carácter público o privado/asociativo de la administración de la institución de cuidado alternativo.</t>
       </text>
     </comment>
     <comment ref="D4" authorId="0" shapeId="0">
       <text>
         <t>¿Tiene convenio con el OPN? (Solo para los de gestión no gubernamental y gestión mixta)
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="E4" authorId="0" shapeId="0">
       <text>
         <t>Localidad
-Ciudad, municipio, comuna o localidad geográfica donde se encuentra el dispositivo físicamente.
-Qué se espera: texto
-Máximo 120 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 120 caracteres.
+Ciudad, municipio, comuna o localidad geográfica donde se encuentra el dispositivo físicamente.</t>
       </text>
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
         <t>Dirección
-Domicilio real (calle, número, piso/departamento, entre calles) donde se encuentra ubicada la residencia.
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.
+Domicilio real (calle, número, piso/departamento, entre calles) donde se encuentra ubicada la residencia.</t>
       </text>
     </comment>
     <comment ref="G4" authorId="0" shapeId="0">
       <text>
         <t>Código postal
-Código Postal Argentino de la localidad correspondiente.
-Qué se espera: texto
-Máximo 10 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 10 caracteres.
+Código Postal Argentino de la localidad correspondiente.</t>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
         <t>Teléfono
-Número de contacto telefónico institucional o celular de guardia de la residencia.
-Qué se espera: texto
-Máximo 50 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 50 caracteres.
+Número de contacto telefónico institucional o celular de guardia de la residencia.</t>
       </text>
     </comment>
     <comment ref="I4" authorId="0" shapeId="0">
       <text>
         <t>El dispositivo, ¿registra las intervenciones en el Sistema Nominal digital del OPN provincial?
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
         <t>... Proyecto institucional?
-Qué se espera: texto
-Máximo 31 caracteres.
-Elegir de la lista "... Proyecto institucional?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: esta actualizado y se aplica, esta actualizado y no se aplica, Si, pero esta desactualizado, No, pero esta en diseño.</t>
       </text>
     </comment>
     <comment ref="K4" authorId="0" shapeId="0">
       <text>
         <t>…reglamento de convivencia?
-Qué se espera: texto
-Máximo 31 caracteres.
-Elegir de la lista "... Proyecto institucional?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: esta actualizado y se aplica, esta actualizado y no se aplica, Si, pero esta desactualizado, No, pero esta en diseño.</t>
       </text>
     </comment>
     <comment ref="L4" authorId="0" shapeId="0">
       <text>
         <t>... habilitación municipal?
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "habilitación municipal?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Si, No, En trámite.</t>
       </text>
     </comment>
     <comment ref="M4" authorId="0" shapeId="0">
       <text>
         <t>... con rampas o condiciones para el acceso y circulación de personas con discapacidad
-Qué se espera: texto
-Máximo 38 caracteres.
-Elegir de la lista "... con rampas o condiciones para el acceso y circulación de personas con discapacidad".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí en todos los espacios requeridos, Sí en la mayoría de los espacios, Sí, para algunos pocos espcios, aunque se puede adaptar si lo requiere, No, y no es posible adaptarlos.</t>
       </text>
     </comment>
     <comment ref="N4" authorId="0" shapeId="0">
       <text>
         <t>... tablets o computadoras para los NyA alojados en el dispositivo
-Qué se espera: texto
-Máximo 48 caracteres.
-Elegir de la lista ". tablets o computadoras para los NyA alojados en el dispositivo".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: 1 tablet o computadora por NyA, 1 tablet o computadora por cada 2 a 4 NyA, 1 tablet o computadora por cada 5 NyA o más, No cuentan con tablet o computadora para los NyA.</t>
       </text>
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
         <t>... WIFI en el dispositivo
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="P4" authorId="0" shapeId="0">
       <text>
         <t>... para el ingreso del NyA al dispositivo
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
         <t>…para el abordaje de conflictos o violencia entre NyA
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="R4" authorId="0" shapeId="0">
       <text>
         <t>... para el abordaje de crisis y urgencias en salud mental
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="S4" authorId="0" shapeId="0">
       <text>
         <t>Capacidad de alojamiento (Plazas)
-Cantidad máxima total de plazas (camas) habilitadas formalmente por el dispositivo para el alojamiento de NyA.
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Cantidad máxima total de plazas (camas) habilitadas formalmente por el dispositivo para el alojamiento de NyA.</t>
       </text>
     </comment>
     <comment ref="T4" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de NyA alojados en el dispositivo (al momento de la carga de la información)
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 0 y 200.
+Entre 0 y 5000.</t>
       </text>
     </comment>
     <comment ref="U4" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de NyA que es posible alojar por dormitorio
-Distribución edilicia por habitación. Indicar cuántas camas hay en promedio por dormitorio.
-Qué se espera: texto
-Máximo 26 caracteres.
-Elegir de la lista "Cantidad de NyA que es posible alojar por dormitorio".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Hasta 4 NyA por dormitorio, Entre 5 y 8 por dormitorio, 9 y más.
+Distribución edilicia por habitación. Indicar cuántas camas hay en promedio por dormitorio.</t>
       </text>
     </comment>
     <comment ref="V4" authorId="0" shapeId="0">
       <text>
         <t>Género admitido
-Perfil de género de la población de NyA que tiene autorización de ingreso al dispositivo.
-Qué se espera: texto
-Máximo 39 caracteres.
-Elegir de la lista "Género admitido".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Aloja solo niñas y adolescentes mujeres, Aloja solo niños y adolescente varones, Aloja niños niñas y adolescentes.
+Perfil de género de la población de NyA que tiene autorización de ingreso al dispositivo.</t>
       </text>
     </comment>
     <comment ref="W4" authorId="0" shapeId="0">
       <text>
         <t>grupos de hermanos?
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="X4" authorId="0" shapeId="0">
       <text>
         <t>NyA dolescentes con discapacidad
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="Y4" authorId="0" shapeId="0">
       <text>
         <t>NyA con padecimiento de salud mental
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="Z4" authorId="0" shapeId="0">
       <text>
         <t>NyA con uso o abuso de sustancias
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AA4" authorId="0" shapeId="0">
       <text>
         <t>Adolescentes con hijos
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AB4" authorId="0" shapeId="0">
       <text>
         <t>Aloja niños de 0 a 5 años
-Indica si el dispositivo admite y aloja a niños en la primera infancia (0 a 5 años inclusive).
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.
+Indica si el dispositivo admite y aloja a niños en la primera infancia (0 a 5 años inclusive).</t>
       </text>
     </comment>
     <comment ref="AC4" authorId="0" shapeId="0">
       <text>
         <t>Aloja niños de 6 a 12 años
-Indica si el dispositivo admite y aloja a niños en edad escolar primaria (6 a 12 años inclusive).
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.
+Indica si el dispositivo admite y aloja a niños en edad escolar primaria (6 a 12 años inclusive).</t>
       </text>
     </comment>
     <comment ref="AD4" authorId="0" shapeId="0">
       <text>
         <t>Aloja población de 13 a 17 años
-Indica si el dispositivo admite y aloja a adolescentes de 13 a 17 años inclusive.
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.
+Indica si el dispositivo admite y aloja a adolescentes de 13 a 17 años inclusive.</t>
       </text>
     </comment>
     <comment ref="AE4" authorId="0" shapeId="0">
       <text>
         <t>Aloja población de 18 años y más
-Indica si excepcionalmente aloja a jóvenes de 18 años o más que continúan en tránsito de egreso o bajo prórroga legal de protección.
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.
+Indica si excepcionalmente aloja a jóvenes de 18 años o más que continúan en tránsito de egreso o bajo prórroga legal de protección.</t>
       </text>
     </comment>
     <comment ref="AF4" authorId="0" shapeId="0">
       <text>
         <t>… que conforman el equipo técnico
-Qué se espera: texto
-Máximo 28 caracteres.
-Elegir de la lista "… que conforman el equipo técnico".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: 1, 2, 3, 4, 5, 6 o más personas, No cuenta con equipo técnico.</t>
       </text>
     </comment>
     <comment ref="AG4" authorId="0" shapeId="0">
       <text>
         <t>... destinadas al cuidado del NyA
-Qué se espera: texto
-Máximo 32 caracteres.
-Elegir de la lista "... destinadas al cuidado del NyA".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: 9 opciones, en el desplegable.</t>
       </text>
     </comment>
     <comment ref="AH4" authorId="0" shapeId="0">
       <text>
         <t>... destinadas a tareas de apoyo (administrativo, mantenimiento, cocina, etc)
-Qué se espera: texto
-Máximo 31 caracteres.
-Elegir de la lista "... destinadas a tareas de apoyo (administrativo, mantenimiento, cocina, etc)".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: 9 opciones, en el desplegable.</t>
       </text>
     </comment>
     <comment ref="AI4" authorId="0" shapeId="0">
       <text>
         <t>… del equipo de conducción
-Qué se espera: texto
-Máximo 36 caracteres.
-Elegir de la lista "del equipo de conducción".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: 1, 2, 3 o más personas, No cuenta con personal de conducción.</t>
       </text>
     </comment>
     <comment ref="AJ4" authorId="0" shapeId="0">
       <text>
         <t>Recibió capacitación en PROMOCION DE CUIDADOS
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AK4" authorId="0" shapeId="0">
       <text>
         <t>Recibió capacitación en ALIMENTACION SALUDABLE
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AL4" authorId="0" shapeId="0">
       <text>
         <t>Recibió capacitación en REANIMACION CARDIOPULMONAR
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AM4" authorId="0" shapeId="0">
       <text>
         <t>Recibió capacitación en PRIMEROS AUXILIOS
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AN4" authorId="0" shapeId="0">
       <text>
         <t>Recibió capacitación en ABUSO SEXUAL INFANTIL /JUVENIL
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AO4" authorId="0" shapeId="0">
       <text>
         <t>Recibió capacitación en PARADIGMA DE PROTECCION INTEGRAL
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AP4" authorId="0" shapeId="0">
       <text>
         <t>Recibió capacitación en AUTONOMIA PROGRESIVA
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AQ4" authorId="0" shapeId="0">
       <text>
         <t>Recibió capacitación en ABORDAJE EN SALUD MENTAL
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AR4" authorId="0" shapeId="0">
       <text>
         <t>Recibió capacitación en CONSUMOS PROBLEMATICOS
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AS4" authorId="0" shapeId="0">
       <text>
         <t>Recibió capacitación en CULTURA DIGITAL
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AT4" authorId="0" shapeId="0">
       <text>
         <t>Recibió capacitación en DISCAPACIDAD
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AU4" authorId="0" shapeId="0">
       <text>
         <t>Recibió capacitación en ADMINISTRACION FINANCIERA
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AV4" authorId="0" shapeId="0">
       <text>
         <t>Recibió capacitación en OTRAS TEMÁTICAS
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AW4" authorId="0" shapeId="0">
       <text>
         <t>Otras temáticas. Especifique
-Si se marcó 'Sí' en la columna de capacitación en 'OTRAS TEMÁTICAS', especificar aquí cuáles fueron los temas abordados de forma sintética.
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.
+Si se marcó 'Sí' en la columna de capacitación en 'OTRAS TEMÁTICAS', especificar aquí cuáles fueron los temas abordados de forma sintética.</t>
       </text>
     </comment>
     <comment ref="AX4" authorId="0" shapeId="0">
       <text>
         <t>El dipositivo participa en la formulación del proyecto de restitución de derechos
-Qué se espera: texto
-Máximo 34 caracteres.
-Elegir de la lista "El dipositivo participa en la formulación del proyecto de restitución de derechos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: en todas las situaciones, en la mayoría de las situaciones, Sí, en algunas situaciones, No se realiza desde el dispositivo.</t>
       </text>
     </comment>
     <comment ref="AY4" authorId="0" shapeId="0">
       <text>
         <t>Participa el NyA en el proyecto de restitución de derechos (PER)
-Qué se espera: texto
-Máximo 32 caracteres.
-Elegir de la lista "Participa el NyA en el proyecto de restitución de derechos (PER)".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: en todas las situaciones, en la mayoría de las situaciones, Sí, en algunas situaciones, No en ninguna situación.</t>
       </text>
     </comment>
     <comment ref="AZ4" authorId="0" shapeId="0">
       <text>
         <t>Existe articulación entre el PER y el plan de estadía?
-¿Las actividades cotidianas del NyA en el dispositivo están alineadas y coordinadas con el proyecto de restitución trazado por la autoridad de aplicación?
-Qué se espera: texto
-Máximo 32 caracteres.
-Elegir de la lista "Participa el NyA en el proyecto de restitución de derechos (PER)".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: en todas las situaciones, en la mayoría de las situaciones, Sí, en algunas situaciones, No en ninguna situación.
+¿Las actividades cotidianas del NyA en el dispositivo están alineadas y coordinadas con el proyecto de restitución trazado por la autoridad de aplicación?</t>
       </text>
     </comment>
     <comment ref="BA4" authorId="0" shapeId="0">
       <text>
         <t>¿Promueve el contacto con la familia y/o referentes afectivos a través de redes, mails, cartas?
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="BB4" authorId="0" shapeId="0">
       <text>
         <t>¿Promueve el contacto con la familia y/o referentes afectivos a través de encuentros fuera del dispositivo?
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="BC4" authorId="0" shapeId="0">
       <text>
         <t>¿Promueve el contacto con la familia y/o referentes afectivos a través de visitas presenciales?
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="BD4" authorId="0" shapeId="0">
       <text>
         <t>¿Promueve el contacto con la familia y/o referentes afectivos a través de llamadas y videollamadas?
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="BE4" authorId="0" shapeId="0">
       <text>
         <t>¿Con que frecuencia los NyA alojados en el dispositivo realizan actividades fuera del dispositivo?
-Qué se espera: texto
-Máximo 26 caracteres.
-Elegir de la lista "¿Con que frecuencia los NyA alojados en el dispositivo realizan actividades fuera del dispositivo?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: 1 vez por semana o más, Entre 1 y 3 veces por mes, Menos de 1 vez en el mes, No realizan esta actividad.</t>
       </text>
     </comment>
     <comment ref="BF4" authorId="0" shapeId="0">
       <text>
         <t>¿Con que frecuencia los NyA alojados en el dispositivo realizan Actividades ARTISTICAS?
-Qué se espera: texto
-Máximo 26 caracteres.
-Elegir de la lista "¿Con que frecuencia los NyA alojados en el dispositivo realizan actividades fuera del dispositivo?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: 1 vez por semana o más, Entre 1 y 3 veces por mes, Menos de 1 vez en el mes, No realizan esta actividad.</t>
       </text>
     </comment>
     <comment ref="BG4" authorId="0" shapeId="0">
       <text>
         <t>¿Con que frecuencia los NyA alojados en el dispositivo realizan Actividades DEPORTIVAS?
-Qué se espera: texto
-Máximo 26 caracteres.
-Elegir de la lista "¿Con que frecuencia los NyA alojados en el dispositivo realizan actividades fuera del dispositivo?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: 1 vez por semana o más, Entre 1 y 3 veces por mes, Menos de 1 vez en el mes, No realizan esta actividad.</t>
       </text>
     </comment>
     <comment ref="BH4" authorId="0" shapeId="0">
       <text>
         <t>¿Con que frecuencia los NyA alojados en el dispositivo realizan Actividades RECREATIVAS?
-Qué se espera: texto
-Máximo 26 caracteres.
-Elegir de la lista "¿Con que frecuencia los NyA alojados en el dispositivo realizan actividades fuera del dispositivo?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: 1 vez por semana o más, Entre 1 y 3 veces por mes, Menos de 1 vez en el mes, No realizan esta actividad.</t>
       </text>
     </comment>
     <comment ref="BI4" authorId="0" shapeId="0">
       <text>
         <t>¿Con que frecuencia los NyA alojados en el dispositivo realizan OTRAS Actividades?
-Qué se espera: texto
-Máximo 26 caracteres.
-Elegir de la lista "¿Con que frecuencia los NyA alojados en el dispositivo realizan actividades fuera del dispositivo?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: 1 vez por semana o más, Entre 1 y 3 veces por mes, Menos de 1 vez en el mes, No realizan esta actividad.</t>
       </text>
     </comment>
   </commentList>
@@ -12693,160 +12626,160 @@
   </mergeCells>
   <dataValidations count="52">
     <dataValidation sqref="C5:C204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Tipo de gestión&quot;." promptTitle="Tipo de gestión" prompt="Carácter público o privado/asociativo de la administración de la institución de cuidado alternativo." type="list">
-      <formula1>LISTAS!$O$2:$O$4</formula1>
+      <formula1>Listas!$O$2:$O$4</formula1>
     </dataValidation>
     <dataValidation sqref="D5:D204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Tiene convenio con el OPN? (Solo para los de gestión no gubernamental y gestión mixta)&quot;." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="I5:I204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;El dispositivo, ¿registra las intervenciones en el Sistema Nominal digital del OPN provincial?&quot;." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="J5:J204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;... Proyecto institucional?&quot;." type="list">
-      <formula1>LISTAS!$K$2:$K$7</formula1>
+      <formula1>Listas!$K$2:$K$7</formula1>
     </dataValidation>
     <dataValidation sqref="K5:K204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;…reglamento de convivencia?&quot;." type="list">
-      <formula1>LISTAS!$K$2:$K$7</formula1>
+      <formula1>Listas!$K$2:$K$7</formula1>
     </dataValidation>
     <dataValidation sqref="L5:L204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;... habilitación municipal?&quot;." type="list">
-      <formula1>LISTAS!$I$2:$I$4</formula1>
+      <formula1>Listas!$I$2:$I$4</formula1>
     </dataValidation>
     <dataValidation sqref="M5:M204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;... con rampas o condiciones para el acceso y circulación de personas con discapacidad&quot;." type="list">
-      <formula1>LISTAS!$C$2:$C$8</formula1>
+      <formula1>Listas!$C$2:$C$8</formula1>
     </dataValidation>
     <dataValidation sqref="N5:N204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;... tablets o computadoras para los NyA alojados en el dispositivo&quot;." type="list">
-      <formula1>LISTAS!$N$2:$N$5</formula1>
+      <formula1>Listas!$N$2:$N$5</formula1>
     </dataValidation>
     <dataValidation sqref="O5:O204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;... WIFI en el dispositivo&quot;." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="P5:P204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;... para el ingreso del NyA al dispositivo&quot;." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="Q5:Q204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;…para el abordaje de conflictos o violencia entre NyA&quot;." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="R5:R204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;... para el abordaje de crisis y urgencias en salud mental&quot;." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="U5:U204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cantidad de NyA que es posible alojar por dormitorio&quot;." promptTitle="Cantidad de NyA que es posible a" prompt="Distribución edilicia por habitación. Indicar cuántas camas hay en promedio por dormitorio." type="list">
-      <formula1>LISTAS!$A$2:$A$4</formula1>
+      <formula1>Listas!$A$2:$A$4</formula1>
     </dataValidation>
     <dataValidation sqref="V5:V204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Género admitido&quot;." promptTitle="Género admitido" prompt="Perfil de género de la población de NyA que tiene autorización de ingreso al dispositivo." type="list">
-      <formula1>LISTAS!$H$2:$H$4</formula1>
+      <formula1>Listas!$H$2:$H$4</formula1>
     </dataValidation>
     <dataValidation sqref="W5:W204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;grupos de hermanos?&quot;." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="X5:X204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;NyA dolescentes con discapacidad&quot;." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="Y5:Y204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;NyA con padecimiento de salud mental&quot;." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="Z5:Z204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;NyA con uso o abuso de sustancias&quot;." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="AA5:AA204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Adolescentes con hijos&quot;." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="AB5:AB204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Aloja niños de 0 a 5 años&quot;." promptTitle="Aloja niños de 0 a 5 años" prompt="Indica si el dispositivo admite y aloja a niños en la primera infancia (0 a 5 años inclusive)." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="AC5:AC204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Aloja niños de 6 a 12 años&quot;." promptTitle="Aloja niños de 6 a 12 años" prompt="Indica si el dispositivo admite y aloja a niños en edad escolar primaria (6 a 12 años inclusive)." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="AD5:AD204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Aloja población de 13 a 17 años&quot;." promptTitle="Aloja población de 13 a 17 años" prompt="Indica si el dispositivo admite y aloja a adolescentes de 13 a 17 años inclusive." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="AE5:AE204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Aloja población de 18 años y más&quot;." promptTitle="Aloja población de 18 años y más" prompt="Indica si excepcionalmente aloja a jóvenes de 18 años o más que continúan en tránsito de egreso o bajo prórroga legal de protección." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="AF5:AF204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;… que conforman el equipo técnico&quot;." type="list">
-      <formula1>LISTAS!$L$2:$L$8</formula1>
+      <formula1>Listas!$L$2:$L$8</formula1>
     </dataValidation>
     <dataValidation sqref="AG5:AG204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;... destinadas al cuidado del NyA&quot;." type="list">
-      <formula1>LISTAS!$F$2:$F$10</formula1>
+      <formula1>Listas!$F$2:$F$10</formula1>
     </dataValidation>
     <dataValidation sqref="AH5:AH204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;... destinadas a tareas de apoyo (administrativo, mantenimiento, cocina, etc)&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$10</formula1>
+      <formula1>Listas!$E$2:$E$10</formula1>
     </dataValidation>
     <dataValidation sqref="AI5:AI204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;… del equipo de conducción&quot;." type="list">
-      <formula1>LISTAS!$D$2:$D$5</formula1>
+      <formula1>Listas!$D$2:$D$5</formula1>
     </dataValidation>
     <dataValidation sqref="AJ5:AJ204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Recibió capacitación en PROMOCION DE CUIDADOS&quot;." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="AK5:AK204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Recibió capacitación en ALIMENTACION SALUDABLE&quot;." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="AL5:AL204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Recibió capacitación en REANIMACION CARDIOPULMONAR&quot;." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="AM5:AM204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Recibió capacitación en PRIMEROS AUXILIOS&quot;." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="AN5:AN204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Recibió capacitación en ABUSO SEXUAL INFANTIL /JUVENIL&quot;." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="AO5:AO204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Recibió capacitación en PARADIGMA DE PROTECCION INTEGRAL&quot;." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="AP5:AP204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Recibió capacitación en AUTONOMIA PROGRESIVA&quot;." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="AQ5:AQ204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Recibió capacitación en ABORDAJE EN SALUD MENTAL&quot;." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="AR5:AR204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Recibió capacitación en CONSUMOS PROBLEMATICOS&quot;." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="AS5:AS204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Recibió capacitación en CULTURA DIGITAL&quot;." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="AT5:AT204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Recibió capacitación en DISCAPACIDAD&quot;." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="AU5:AU204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Recibió capacitación en ADMINISTRACION FINANCIERA&quot;." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="AV5:AV204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Recibió capacitación en OTRAS TEMÁTICAS&quot;." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="AX5:AX204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;El dipositivo participa en la formulación del proyecto de restitución de derechos&quot;." type="list">
-      <formula1>LISTAS!$G$2:$G$6</formula1>
+      <formula1>Listas!$G$2:$G$6</formula1>
     </dataValidation>
     <dataValidation sqref="AY5:AY204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Participa el NyA en el proyecto de restitución de derechos (PER)&quot;." type="list">
-      <formula1>LISTAS!$J$2:$J$6</formula1>
+      <formula1>Listas!$J$2:$J$6</formula1>
     </dataValidation>
     <dataValidation sqref="AZ5:AZ204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Existe articulación entre el PER y el plan de estadía?&quot;." promptTitle="Existe articulación entre el PER" prompt="¿Las actividades cotidianas del NyA en el dispositivo están alineadas y coordinadas con el proyecto de restitución trazado por la autoridad de aplicación?" type="list">
-      <formula1>LISTAS!$J$2:$J$6</formula1>
+      <formula1>Listas!$J$2:$J$6</formula1>
     </dataValidation>
     <dataValidation sqref="BA5:BA204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Promueve el contacto con la familia y/o referentes afectivos a través de redes, mails, cartas?&quot;." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="BB5:BB204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Promueve el contacto con la familia y/o referentes afectivos a través de encuentros fuera del dispositivo?&quot;." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="BC5:BC204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Promueve el contacto con la familia y/o referentes afectivos a través de visitas presenciales?&quot;." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="BD5:BD204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Promueve el contacto con la familia y/o referentes afectivos a través de llamadas y videollamadas?&quot;." type="list">
-      <formula1>LISTAS!$M$2:$M$4</formula1>
+      <formula1>Listas!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="BE5:BE204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Con que frecuencia los NyA alojados en el dispositivo realizan actividades fuera del dispositivo?&quot;." type="list">
-      <formula1>LISTAS!$B$2:$B$5</formula1>
+      <formula1>Listas!$B$2:$B$5</formula1>
     </dataValidation>
     <dataValidation sqref="BF5:BF204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Con que frecuencia los NyA alojados en el dispositivo realizan Actividades ARTISTICAS?&quot;." type="list">
-      <formula1>LISTAS!$B$2:$B$5</formula1>
+      <formula1>Listas!$B$2:$B$5</formula1>
     </dataValidation>
     <dataValidation sqref="BG5:BG204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Con que frecuencia los NyA alojados en el dispositivo realizan Actividades DEPORTIVAS?&quot;." type="list">
-      <formula1>LISTAS!$B$2:$B$5</formula1>
+      <formula1>Listas!$B$2:$B$5</formula1>
     </dataValidation>
     <dataValidation sqref="BH5:BH204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Con que frecuencia los NyA alojados en el dispositivo realizan Actividades RECREATIVAS?&quot;." type="list">
-      <formula1>LISTAS!$B$2:$B$5</formula1>
+      <formula1>Listas!$B$2:$B$5</formula1>
     </dataValidation>
     <dataValidation sqref="BI5:BI204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Con que frecuencia los NyA alojados en el dispositivo realizan OTRAS Actividades?&quot;." type="list">
-      <formula1>LISTAS!$B$2:$B$5</formula1>
+      <formula1>Listas!$B$2:$B$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12855,842 +12788,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B72"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>Campo</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>Indicación para el llenado</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>Hoja: M Residencial</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>Datos institucionales</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Nombre del dispositvo</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Dependencia institucional</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>Organismo, ministerio, secretaría, dirección o área estatal de la cual depende orgánica y formalmente el dispositivo de cuidado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Tipo de gestión</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Carácter público o privado/asociativo de la administración de la institución de cuidado alternativo.
-Debe elegirse un valor de la lista "Tipo de gestión".</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>¿Tiene convenio con el OPN? (Solo para los de gestión no gubernamental y gestión mixta)</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Localidad</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>Ciudad, municipio, comuna o localidad geográfica donde se encuentra el dispositivo físicamente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Dirección</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Domicilio real (calle, número, piso/departamento, entre calles) donde se encuentra ubicada la residencia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Código postal</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Código Postal Argentino de la localidad correspondiente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Teléfono</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Número de contacto telefónico institucional o celular de guardia de la residencia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>El dispositivo, ¿registra las intervenciones en el Sistema Nominal digital del OPN provincial?</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>El establecimiento cuenta con...</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>... Proyecto institucional?</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "... Proyecto institucional?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>…reglamento de convivencia?</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "... Proyecto institucional?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>... habilitación municipal?</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "habilitación municipal?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>... con rampas o condiciones para el acceso y circulación de personas con discapacidad</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "... con rampas o condiciones para el acceso y circulación de personas con discapacidad".</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>... tablets o computadoras para los NyA alojados en el dispositivo</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista ". tablets o computadoras para los NyA alojados en el dispositivo".</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>... WIFI en el dispositivo</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>Cuenta con PROTOCOLO ...</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>... para el ingreso del NyA al dispositivo</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>…para el abordaje de conflictos o violencia entre NyA</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>... para el abordaje de crisis y urgencias en salud mental</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>Capacidad /cobertura</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Capacidad de alojamiento (Plazas)</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>Cantidad máxima total de plazas (camas) habilitadas formalmente por el dispositivo para el alojamiento de NyA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Cantidad de NyA alojados en el dispositivo (al momento de la carga de la información)</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Cantidad de NyA que es posible alojar por dormitorio</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>Distribución edilicia por habitación. Indicar cuántas camas hay en promedio por dormitorio.
-Debe elegirse un valor de la lista "Cantidad de NyA que es posible alojar por dormitorio".</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>Perfiles poblacionales admitidos</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Género admitido</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>Perfil de género de la población de NyA que tiene autorización de ingreso al dispositivo.
-Debe elegirse un valor de la lista "Género admitido".</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>grupos de hermanos?</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>NyA dolescentes con discapacidad</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>NyA con padecimiento de salud mental</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>NyA con uso o abuso de sustancias</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Adolescentes con hijos</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Aloja niños de 0 a 5 años</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>Indica si el dispositivo admite y aloja a niños en la primera infancia (0 a 5 años inclusive).
-Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Aloja niños de 6 a 12 años</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>Indica si el dispositivo admite y aloja a niños en edad escolar primaria (6 a 12 años inclusive).
-Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Aloja población de 13 a 17 años</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>Indica si el dispositivo admite y aloja a adolescentes de 13 a 17 años inclusive.
-Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Aloja población de 18 años y más</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>Indica si excepcionalmente aloja a jóvenes de 18 años o más que continúan en tránsito de egreso o bajo prórroga legal de protección.
-Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>Personal del dispositivo: CANTIDAD DE PERSONAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>… que conforman el equipo técnico</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "… que conforman el equipo técnico".</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>... destinadas al cuidado del NyA</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "... destinadas al cuidado del NyA".</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>... destinadas a tareas de apoyo (administrativo, mantenimiento, cocina, etc)</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "... destinadas a tareas de apoyo (administrativo, mantenimiento, cocina, etc)".</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>… del equipo de conducción</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "del equipo de conducción".</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>CAPACITACIONES RECIBIDAS POR EL PERSONAL QUE TRABAJA EN EL DISPOSITIVO EN EL ÚLTIMO AÑO</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Recibió capacitación en PROMOCION DE CUIDADOS</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Recibió capacitación en ALIMENTACION SALUDABLE</t>
-        </is>
-      </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Recibió capacitación en REANIMACION CARDIOPULMONAR</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Recibió capacitación en PRIMEROS AUXILIOS</t>
-        </is>
-      </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Recibió capacitación en ABUSO SEXUAL INFANTIL /JUVENIL</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Recibió capacitación en PARADIGMA DE PROTECCION INTEGRAL</t>
-        </is>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Recibió capacitación en AUTONOMIA PROGRESIVA</t>
-        </is>
-      </c>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Recibió capacitación en ABORDAJE EN SALUD MENTAL</t>
-        </is>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Recibió capacitación en CONSUMOS PROBLEMATICOS</t>
-        </is>
-      </c>
-      <c r="B53" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Recibió capacitación en CULTURA DIGITAL</t>
-        </is>
-      </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Recibió capacitación en DISCAPACIDAD</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Recibió capacitación en ADMINISTRACION FINANCIERA</t>
-        </is>
-      </c>
-      <c r="B56" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Recibió capacitación en OTRAS TEMÁTICAS</t>
-        </is>
-      </c>
-      <c r="B57" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Otras temáticas. Especifique</t>
-        </is>
-      </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>Si se marcó 'Sí' en la columna de capacitación en 'OTRAS TEMÁTICAS', especificar aquí cuáles fueron los temas abordados de forma sintética.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="8" t="inlineStr">
-        <is>
-          <t>SOBRE EL PROYECTO DE RESTITUCIÓN DE DERECHOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>El dipositivo participa en la formulación del proyecto de restitución de derechos</t>
-        </is>
-      </c>
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "El dipositivo participa en la formulación del proyecto de restitución de derechos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Participa el NyA en el proyecto de restitución de derechos (PER)</t>
-        </is>
-      </c>
-      <c r="B61" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Participa el NyA en el proyecto de restitución de derechos (PER)".</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Existe articulación entre el PER y el plan de estadía?</t>
-        </is>
-      </c>
-      <c r="B62" s="9" t="inlineStr">
-        <is>
-          <t>¿Las actividades cotidianas del NyA en el dispositivo están alineadas y coordinadas con el proyecto de restitución trazado por la autoridad de aplicación?
-Debe elegirse un valor de la lista "Participa el NyA en el proyecto de restitución de derechos (PER)".</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="8" t="inlineStr">
-        <is>
-          <t>INSERCIÓN FAMILIAR Y COMUNITARIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>¿Promueve el contacto con la familia y/o referentes afectivos a través de redes, mails, cartas?</t>
-        </is>
-      </c>
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>¿Promueve el contacto con la familia y/o referentes afectivos a través de encuentros fuera del dispositivo?</t>
-        </is>
-      </c>
-      <c r="B65" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>¿Promueve el contacto con la familia y/o referentes afectivos a través de visitas presenciales?</t>
-        </is>
-      </c>
-      <c r="B66" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>¿Promueve el contacto con la familia y/o referentes afectivos a través de llamadas y videollamadas?</t>
-        </is>
-      </c>
-      <c r="B67" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>¿Con que frecuencia los NyA alojados en el dispositivo realizan actividades fuera del dispositivo?</t>
-        </is>
-      </c>
-      <c r="B68" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Con que frecuencia los NyA alojados en el dispositivo realizan actividades fuera del dispositivo?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>¿Con que frecuencia los NyA alojados en el dispositivo realizan Actividades ARTISTICAS?</t>
-        </is>
-      </c>
-      <c r="B69" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Con que frecuencia los NyA alojados en el dispositivo realizan actividades fuera del dispositivo?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>¿Con que frecuencia los NyA alojados en el dispositivo realizan Actividades DEPORTIVAS?</t>
-        </is>
-      </c>
-      <c r="B70" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Con que frecuencia los NyA alojados en el dispositivo realizan actividades fuera del dispositivo?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>¿Con que frecuencia los NyA alojados en el dispositivo realizan Actividades RECREATIVAS?</t>
-        </is>
-      </c>
-      <c r="B71" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Con que frecuencia los NyA alojados en el dispositivo realizan actividades fuera del dispositivo?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>¿Con que frecuencia los NyA alojados en el dispositivo realizan OTRAS Actividades?</t>
-        </is>
-      </c>
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Con que frecuencia los NyA alojados en el dispositivo realizan actividades fuera del dispositivo?".</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14191,7 +13288,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
